--- a/e2e/expectedData/sub_Master_Daftar_Gaji.xlsx
+++ b/e2e/expectedData/sub_Master_Daftar_Gaji.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="31">
   <si>
     <t>NIK</t>
   </si>
@@ -47,61 +47,67 @@
     <t>TOTAL</t>
   </si>
   <si>
+    <t>DIAN EVIYANTI APLUGI</t>
+  </si>
+  <si>
+    <t>III</t>
+  </si>
+  <si>
+    <t>Expat</t>
+  </si>
+  <si>
+    <t>AHMAD RIYANA SAPUTRA</t>
+  </si>
+  <si>
+    <t>IV</t>
+  </si>
+  <si>
+    <t>CLAUDIO DA COSTA ALVES</t>
+  </si>
+  <si>
+    <t>VI</t>
+  </si>
+  <si>
+    <t>Outsource</t>
+  </si>
+  <si>
+    <t>CELIA MARIA REGO DE FATIMA</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>FRIESCA AMELIA</t>
+  </si>
+  <si>
+    <t>RIMBUN SIBURIAN</t>
+  </si>
+  <si>
+    <t>1,050</t>
+  </si>
+  <si>
+    <t>Lestari Putri Cantika</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>Homestaff</t>
+  </si>
+  <si>
+    <t>HERU YULIANTO</t>
+  </si>
+  <si>
+    <t>II</t>
+  </si>
+  <si>
+    <t>SYALDY KHARISMA ANANDA</t>
+  </si>
+  <si>
+    <t>AGOSTINHO GOMES FERNANDES</t>
+  </si>
+  <si>
     <t>ADROALDINO DA SILVA NORONHA TOME</t>
-  </si>
-  <si>
-    <t>VI</t>
-  </si>
-  <si>
-    <t>Expat</t>
-  </si>
-  <si>
-    <t>AGOSTINHO GOMES FERNANDES</t>
-  </si>
-  <si>
-    <t>CELIA MARIA REGO DE FATIMA</t>
-  </si>
-  <si>
-    <t>IV</t>
-  </si>
-  <si>
-    <t>CLAUDIO DA COSTA ALVES</t>
-  </si>
-  <si>
-    <t>DIAN EVIYANTI APLUGI</t>
-  </si>
-  <si>
-    <t>III</t>
-  </si>
-  <si>
-    <t>AHMAD RIYANA SAPUTRA</t>
-  </si>
-  <si>
-    <t>FRIESCA AMELIA</t>
-  </si>
-  <si>
-    <t>HERU YULIANTO</t>
-  </si>
-  <si>
-    <t>II</t>
-  </si>
-  <si>
-    <t>Homestaff</t>
-  </si>
-  <si>
-    <t>RIMBUN SIBURIAN</t>
-  </si>
-  <si>
-    <t>1,050</t>
-  </si>
-  <si>
-    <t>SYALDY KHARISMA ANANDA</t>
-  </si>
-  <si>
-    <t>Lestari Putri Cantika</t>
-  </si>
-  <si>
-    <t>V</t>
   </si>
 </sst>
 </file>
@@ -490,7 +496,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2">
-        <v>24016</v>
+        <v>79001</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -502,39 +508,39 @@
         <v>12</v>
       </c>
       <c r="E2">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>180</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3">
-        <v>26013</v>
+        <v>95008</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
       <c r="E3">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="F3">
         <v>10</v>
@@ -546,30 +552,30 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4">
-        <v>92003</v>
+        <v>24005</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E4">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -581,27 +587,27 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>340</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5">
-        <v>24005</v>
+        <v>92003</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E5">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="F5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -613,27 +619,27 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>210</v>
+        <v>340</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6">
-        <v>79001</v>
+        <v>91009</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
       </c>
       <c r="E6">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F6">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="G6">
         <v>50</v>
@@ -645,27 +651,27 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>300</v>
+        <v>700</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7">
-        <v>95008</v>
+        <v>81010</v>
       </c>
       <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
         <v>19</v>
       </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
       <c r="E7">
-        <v>510</v>
+        <v>850</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -676,40 +682,40 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
-        <v>520</v>
+      <c r="J7" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8">
-        <v>91009</v>
+        <v>999999</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E8">
         <v>500</v>
       </c>
       <c r="F8">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>700</v>
+        <v>504</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -717,13 +723,13 @@
         <v>74003</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E9">
         <v>500</v>
@@ -746,98 +752,98 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10">
-        <v>81010</v>
+        <v>91015</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E10">
-        <v>850</v>
+        <v>200</v>
       </c>
       <c r="F10">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10" t="s">
-        <v>25</v>
+        <v>30</v>
+      </c>
+      <c r="J10">
+        <v>300</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11">
-        <v>91015</v>
+        <v>26013</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E11">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F11">
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
         <v>50</v>
       </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>20</v>
-      </c>
-      <c r="I11">
-        <v>30</v>
-      </c>
       <c r="J11">
-        <v>300</v>
+        <v>560</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12">
-        <v>999999</v>
+        <v>24016</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E12">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="J12">
-        <v>504</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>

--- a/e2e/expectedData/sub_Master_Daftar_Gaji.xlsx
+++ b/e2e/expectedData/sub_Master_Daftar_Gaji.xlsx
@@ -47,67 +47,67 @@
     <t>TOTAL</t>
   </si>
   <si>
+    <t>FRIESCA AMELIA</t>
+  </si>
+  <si>
+    <t>III</t>
+  </si>
+  <si>
+    <t>Expat</t>
+  </si>
+  <si>
+    <t>Lestari Putri Cantika</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>Homestaff</t>
+  </si>
+  <si>
+    <t>HERU YULIANTO</t>
+  </si>
+  <si>
+    <t>II</t>
+  </si>
+  <si>
+    <t>SYALDY KHARISMA ANANDA</t>
+  </si>
+  <si>
+    <t>AGOSTINHO GOMES FERNANDES</t>
+  </si>
+  <si>
+    <t>VI</t>
+  </si>
+  <si>
+    <t>ADROALDINO DA SILVA NORONHA TOME</t>
+  </si>
+  <si>
+    <t>Outsource</t>
+  </si>
+  <si>
+    <t>CELIA MARIA REGO DE FATIMA</t>
+  </si>
+  <si>
+    <t>IV</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>CLAUDIO DA COSTA ALVES</t>
+  </si>
+  <si>
     <t>DIAN EVIYANTI APLUGI</t>
   </si>
   <si>
-    <t>III</t>
-  </si>
-  <si>
-    <t>Expat</t>
-  </si>
-  <si>
     <t>AHMAD RIYANA SAPUTRA</t>
   </si>
   <si>
-    <t>IV</t>
-  </si>
-  <si>
-    <t>CLAUDIO DA COSTA ALVES</t>
-  </si>
-  <si>
-    <t>VI</t>
-  </si>
-  <si>
-    <t>Outsource</t>
-  </si>
-  <si>
-    <t>CELIA MARIA REGO DE FATIMA</t>
-  </si>
-  <si>
-    <t>Local</t>
-  </si>
-  <si>
-    <t>FRIESCA AMELIA</t>
-  </si>
-  <si>
     <t>RIMBUN SIBURIAN</t>
   </si>
   <si>
     <t>1,050</t>
-  </si>
-  <si>
-    <t>Lestari Putri Cantika</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>Homestaff</t>
-  </si>
-  <si>
-    <t>HERU YULIANTO</t>
-  </si>
-  <si>
-    <t>II</t>
-  </si>
-  <si>
-    <t>SYALDY KHARISMA ANANDA</t>
-  </si>
-  <si>
-    <t>AGOSTINHO GOMES FERNANDES</t>
-  </si>
-  <si>
-    <t>ADROALDINO DA SILVA NORONHA TOME</t>
   </si>
 </sst>
 </file>
@@ -496,7 +496,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2">
-        <v>79001</v>
+        <v>91009</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -508,10 +508,10 @@
         <v>12</v>
       </c>
       <c r="E2">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F2">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="G2">
         <v>50</v>
@@ -523,12 +523,12 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>300</v>
+        <v>700</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3">
-        <v>95008</v>
+        <v>999999</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -537,100 +537,100 @@
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>520</v>
+        <v>504</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4">
-        <v>24005</v>
+        <v>74003</v>
       </c>
       <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
       <c r="E4">
+        <v>500</v>
+      </c>
+      <c r="F4">
         <v>150</v>
       </c>
-      <c r="F4">
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
         <v>50</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
       <c r="I4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>210</v>
+        <v>700</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5">
-        <v>92003</v>
+        <v>91015</v>
       </c>
       <c r="B5" t="s">
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E5">
+        <v>200</v>
+      </c>
+      <c r="F5">
+        <v>50</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>20</v>
+      </c>
+      <c r="I5">
+        <v>30</v>
+      </c>
+      <c r="J5">
         <v>300</v>
-      </c>
-      <c r="F5">
-        <v>30</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>10</v>
-      </c>
-      <c r="J5">
-        <v>340</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6">
-        <v>91009</v>
+        <v>26013</v>
       </c>
       <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
         <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>11</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
@@ -639,39 +639,39 @@
         <v>500</v>
       </c>
       <c r="F6">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
         <v>50</v>
       </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
       <c r="J6">
-        <v>700</v>
+        <v>560</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7">
-        <v>81010</v>
+        <v>24016</v>
       </c>
       <c r="B7" t="s">
         <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E7">
-        <v>850</v>
+        <v>120</v>
       </c>
       <c r="F7">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -680,15 +680,15 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7" t="s">
-        <v>22</v>
+        <v>50</v>
+      </c>
+      <c r="J7">
+        <v>180</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8">
-        <v>999999</v>
+        <v>92003</v>
       </c>
       <c r="B8" t="s">
         <v>23</v>
@@ -700,68 +700,68 @@
         <v>25</v>
       </c>
       <c r="E8">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>504</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9">
-        <v>74003</v>
+        <v>24005</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E9">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="F9">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J9">
-        <v>700</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10">
-        <v>91015</v>
+        <v>79001</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E10">
         <v>200</v>
@@ -770,13 +770,13 @@
         <v>50</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H10">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J10">
         <v>300</v>
@@ -784,19 +784,19 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11">
-        <v>26013</v>
+        <v>95008</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
       </c>
       <c r="E11">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="F11">
         <v>10</v>
@@ -808,42 +808,42 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>560</v>
+        <v>520</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12">
-        <v>24016</v>
+        <v>81010</v>
       </c>
       <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12">
+        <v>850</v>
+      </c>
+      <c r="F12">
+        <v>200</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12" t="s">
         <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12">
-        <v>120</v>
-      </c>
-      <c r="F12">
-        <v>10</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>50</v>
-      </c>
-      <c r="J12">
-        <v>180</v>
       </c>
     </row>
   </sheetData>
